--- a/output/pdf_financials_xlsx/BTT.xlsx
+++ b/output/pdf_financials_xlsx/BTT.xlsx
@@ -7436,46 +7436,46 @@
         </is>
       </c>
       <c r="E118" s="3" t="n">
-        <v>3.531493</v>
+        <v>2.283313</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>5.65169</v>
+        <v>4.836952</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>2.744245</v>
+        <v>1.623916</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>1.140847</v>
+        <v>0.480594</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0.00028</v>
+        <v>-0.238115</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-0.072295</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0.211371</v>
+        <v>-0.711714</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>2.246502</v>
+        <v>1.296974</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0.206563</v>
+        <v>0.026617</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0.554978</v>
+        <v>-1.044345</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>1.937272</v>
+        <v>0.189664</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0.029564</v>
+        <v>-0.303429</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>0.040351</v>
+        <v>-0.254873</v>
       </c>
       <c r="R118" s="3" t="n">
-        <v>0</v>
+        <v>-0.196904</v>
       </c>
     </row>
     <row r="119">
@@ -16937,7 +16937,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>-</t>
@@ -21232,7 +21236,7 @@
         </is>
       </c>
       <c r="S131" s="5" t="n">
-        <v>0.095674</v>
+        <v>-0.095674</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -22538,7 +22542,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/BTT.xlsx
+++ b/output/pdf_financials_xlsx/BTT.xlsx
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.087508</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.022401</v>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
@@ -1068,13 +1068,13 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.000657</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.009089</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.004307</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
@@ -2037,10 +2037,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.747387</v>
+        <v>-0.8348950000000001</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.588454</v>
+        <v>-0.610855</v>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
@@ -2048,13 +2048,13 @@
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-4.042357</v>
+        <v>-4.043014</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-5.338163</v>
+        <v>-5.347252</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-3.126555</v>
+        <v>-3.122248</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-1.486949</v>
@@ -2157,10 +2157,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.747387</v>
+        <v>-0.8348950000000001</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.588454</v>
+        <v>-0.610855</v>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
@@ -2168,13 +2168,13 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-4.03953</v>
+        <v>-4.040187</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-5.335999</v>
+        <v>-5.345088</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-3.12509</v>
+        <v>-3.120783</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-1.485475</v>
@@ -2474,49 +2474,49 @@
         <v>0.758215</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.585399</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.772964</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.04028</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.593407</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.005977</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.057063</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.000232</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.148122</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.005473</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.000391</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.736386</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.10532</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.005845</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.016101</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.798079</v>
       </c>
     </row>
     <row r="35">
@@ -2590,49 +2590,49 @@
         <v>0.758215</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.585399</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.772964</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>1.04028</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.593407</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.005977</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.057063</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.000232</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>1.148122</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.005473</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.000391</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.736386</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.10532</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.005845</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.016101</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.798079</v>
       </c>
     </row>
     <row r="37">
@@ -3286,49 +3286,49 @@
         <v>0.023688</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.594827</v>
+        <v>0.009428000000000001</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.778092</v>
+        <v>0.005128</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.047343</v>
+        <v>0.007063</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.597652</v>
+        <v>0.004245</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.010224</v>
+        <v>0.004247</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.06303599999999999</v>
+        <v>0.005973</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.005062</v>
+        <v>0.00483</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.159624</v>
+        <v>0.011502</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.021308</v>
+        <v>0.015835</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.004793</v>
+        <v>0.004402</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.7396</v>
+        <v>0.003214</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.108534</v>
+        <v>0.003214</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.005845</v>
+        <v>0</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.016101</v>
+        <v>0</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.798079</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -7823,13 +7823,13 @@
         <v>0</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.022407</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.023581</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.022216</v>
       </c>
       <c r="Q124" s="3" t="n">
         <v>0</v>
@@ -7883,13 +7883,13 @@
         <v>0</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.022407</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.023581</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.022216</v>
       </c>
       <c r="Q125" s="3" t="n">
         <v>0</v>
@@ -8695,7 +8695,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -9051,7 +9051,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>-</t>
@@ -11177,7 +11181,11 @@
           <t>Reclamation deposits 15</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -12959,7 +12967,11 @@
           <t>Reclamation deposits 5</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
@@ -13559,7 +13571,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -15082,7 +15098,11 @@
           <t>Reclamation Deposit</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E69" s="5" t="n">
         <v>0.0158</v>
       </c>
@@ -17034,7 +17054,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
@@ -20055,7 +20079,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
           <t>-</t>
@@ -22732,7 +22760,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
           <t>-</t>
@@ -29981,7 +30013,11 @@
           <t>Proceeds from reclamation deposit</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E220" t="inlineStr">
         <is>
           <t>-</t>
@@ -36479,7 +36515,11 @@
           <t>Increase in reclamation deposits</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr"/>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E284" s="5" t="n">
         <v>-0.0025</v>
       </c>
@@ -37592,7 +37632,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -39839,7 +39879,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -40550,7 +40590,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -41344,7 +41384,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -42425,7 +42465,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -43219,7 +43259,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
@@ -43623,7 +43663,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -44857,7 +44897,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
@@ -46572,7 +46612,7 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
@@ -50741,7 +50781,7 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E426" s="5" t="n">

--- a/output/pdf_financials_xlsx/BTT.xlsx
+++ b/output/pdf_financials_xlsx/BTT.xlsx
@@ -4430,13 +4430,13 @@
         <v>0</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.05625</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.048204</v>
       </c>
       <c r="G67" s="3" t="n">
         <v>0</v>
@@ -6948,7 +6948,7 @@
         <v>0</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.002056</v>
       </c>
       <c r="D110" s="1" t="inlineStr">
         <is>
@@ -6956,10 +6956,10 @@
         </is>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.002487</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>0.001368</v>
       </c>
       <c r="G110" s="3" t="n">
         <v>0</v>
@@ -17531,7 +17531,11 @@
           <t>Private placements</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
@@ -31128,7 +31132,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E231" t="inlineStr">
         <is>
           <t>-</t>
@@ -31227,7 +31235,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr"/>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E232" t="inlineStr">
         <is>
           <t>-</t>
@@ -35602,7 +35614,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr"/>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E275" t="inlineStr">
         <is>
           <t>-</t>
@@ -35905,7 +35921,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D278" t="inlineStr"/>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E278" s="5" t="n">
         <v>-0.101698</v>
       </c>
@@ -51286,7 +51306,11 @@
           <t>Future income tax recovery (Note 11)</t>
         </is>
       </c>
-      <c r="D431" t="inlineStr"/>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E431" s="5" t="n">
         <v>0.101698</v>
       </c>
